--- a/supertesteo_resultados.xlsx
+++ b/supertesteo_resultados.xlsx
@@ -7,12 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Resumen_Fuerzas_Internas" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="F_Interna_Global" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Cargas_Globales_en_nudos" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="reacciones_locales_de_empotramiento" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Vector_Nodal_Equivalente" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="f_local_Reacc_i_por_Carga" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="reacciones_de_estructura_Globales" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Desplazamientos_globales_D" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sistema_reducido_Kll_Fl" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Cargas_Globales_en_nudos" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="reacciones_locales_de_empotramiento" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Vector_Nodal_Equivalente" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Ejes_Locales" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Matriz_Rotacion_T" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
@@ -432,25 +432,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="25" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="23" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="12" max="12"/>
     <col width="21" customWidth="1" min="13" max="13"/>
-    <col width="21" customWidth="1" min="14" max="14"/>
-    <col width="23" customWidth="1" min="15" max="15"/>
-    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -471,67 +470,62 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Longitud (cm)</t>
+          <t>Fx_i</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Fx_i (kN)</t>
+          <t>Fy_i</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Fy_i (kN)</t>
+          <t>Fz_i</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Fz_i (kN)</t>
+          <t>Mx_i</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Mx_i (kN·cm)</t>
+          <t>My_i</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>My_i (kN·cm)</t>
+          <t>Mz_i</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Mz_i (kN·cm)</t>
+          <t>Fx_f</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Fx_f (kN)</t>
+          <t>Fy_f</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Fy_f (kN)</t>
+          <t>Fz_f</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Fz_f (kN)</t>
+          <t>Mx_f</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Mx_f (kN·cm)</t>
+          <t>My_f</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>My_f (kN·cm)</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Mz_f (kN·cm)</t>
+          <t>Mz_f</t>
         </is>
       </c>
     </row>
@@ -546,42 +540,39 @@
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>300</v>
+        <v>0.08264608928248485</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1099770941905521</v>
+        <v>0.3132746458246708</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1465176493074707</v>
+        <v>5.080843638685171</v>
       </c>
       <c r="G2" t="n">
-        <v>5.279055776464235</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>3.552713678800501e-15</v>
       </c>
       <c r="I2" t="n">
-        <v>2.664535259100376e-15</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>-0.08264608928248485</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.1099770941905521</v>
+        <v>-0.3132746458246708</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.1465176493074707</v>
+        <v>-5.080843638685171</v>
       </c>
       <c r="M2" t="n">
-        <v>-5.279055776464235</v>
+        <v>-93.98239374740125</v>
       </c>
       <c r="N2" t="n">
-        <v>-43.95529479224122</v>
+        <v>24.79382678474544</v>
       </c>
       <c r="O2" t="n">
-        <v>32.99312825716563</v>
-      </c>
-      <c r="P2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -596,42 +587,39 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>300</v>
+        <v>-2.220446049250313e-16</v>
       </c>
       <c r="E3" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>2.664535259100376e-15</v>
       </c>
       <c r="F3" t="n">
-        <v>-5.000000000000002</v>
+        <v>11.39111351096038</v>
       </c>
       <c r="G3" t="n">
-        <v>11.56576802356741</v>
+        <v>2.273736754432321e-13</v>
       </c>
       <c r="H3" t="n">
-        <v>375</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>2.220446049250313e-16</v>
       </c>
       <c r="K3" t="n">
-        <v>-4.440892098500626e-16</v>
+        <v>4.999999999999997</v>
       </c>
       <c r="L3" t="n">
-        <v>1.77635683940025e-15</v>
+        <v>-11.39111351096038</v>
       </c>
       <c r="M3" t="n">
-        <v>-11.56576802356741</v>
+        <v>749.9999999999998</v>
       </c>
       <c r="N3" t="n">
-        <v>375.0000000000002</v>
+        <v>-4.263256414560601e-14</v>
       </c>
       <c r="O3" t="n">
-        <v>9.947598300641403e-14</v>
-      </c>
-      <c r="P3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -646,43 +634,40 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>200</v>
+        <v>0.08264608928241235</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1099770941904298</v>
+        <v>-4.686725354175329</v>
       </c>
       <c r="F4" t="n">
-        <v>-4.85348235069253</v>
+        <v>6.471957149645529</v>
       </c>
       <c r="G4" t="n">
-        <v>1.844823800031678</v>
+        <v>-656.0176062525985</v>
       </c>
       <c r="H4" t="n">
-        <v>-456.0447052077589</v>
+        <v>-16.70946291623017</v>
       </c>
       <c r="I4" t="n">
-        <v>-5.087550610739213</v>
+        <v>-31.32746458246704</v>
       </c>
       <c r="J4" t="n">
-        <v>-14.65176493074691</v>
+        <v>-0.08264608928241235</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.1099770941904298</v>
+        <v>4.686725354175329</v>
       </c>
       <c r="L4" t="n">
-        <v>4.85348235069253</v>
+        <v>-1.471957149645529</v>
       </c>
       <c r="M4" t="n">
-        <v>-6.844823800031678</v>
+        <v>-138.3738236765075</v>
       </c>
       <c r="N4" t="n">
-        <v>-412.9200547985768</v>
+        <v>16.70946291623017</v>
       </c>
       <c r="O4" t="n">
-        <v>5.087550610739213</v>
-      </c>
-      <c r="P4" t="n">
-        <v>36.64718376883285</v>
+        <v>47.85668243894946</v>
       </c>
     </row>
     <row r="5">
@@ -696,43 +681,40 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>100</v>
+        <v>0.08264608928243433</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1099770941904126</v>
+        <v>0.3132746458246718</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1465176493074694</v>
+        <v>5.080843638685151</v>
       </c>
       <c r="G5" t="n">
-        <v>-4.720944223535734</v>
+        <v>93.98239374740122</v>
       </c>
       <c r="H5" t="n">
-        <v>43.95529479224121</v>
+        <v>-24.79382678474538</v>
       </c>
       <c r="I5" t="n">
-        <v>217.0068717428343</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.4210854715202e-14</v>
+        <v>-0.08264608928243433</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.1099770941904126</v>
+        <v>-0.3132746458246718</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.1465176493074694</v>
+        <v>4.919156361314849</v>
       </c>
       <c r="M5" t="n">
-        <v>-5.279055776464266</v>
+        <v>-93.98239374740122</v>
       </c>
       <c r="N5" t="n">
-        <v>-43.95529479224121</v>
+        <v>16.70946291623029</v>
       </c>
       <c r="O5" t="n">
-        <v>-244.9124493892609</v>
-      </c>
-      <c r="P5" t="n">
-        <v>14.65176493074691</v>
+        <v>31.32746458246709</v>
       </c>
     </row>
   </sheetData>
@@ -746,100 +728,52 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="25" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="21" customWidth="1" min="12" max="12"/>
-    <col width="21" customWidth="1" min="13" max="13"/>
-    <col width="23" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Barra ID</t>
+          <t>Nodo ID</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Nodo Inicial</t>
+          <t>Ux</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Nodo Final</t>
+          <t>Uy</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Fx_i</t>
+          <t>Uz</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Fy_i</t>
+          <t>Rx</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Fz_i</t>
+          <t>Ry</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Mx_i</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>My_i</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Mz_i</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Fx_f</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Fy_f</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Fz_f</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Mx_f</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>My_f</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Mz_f</t>
+          <t>Rz</t>
         </is>
       </c>
     </row>
@@ -848,46 +782,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1099770941905521</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1465176493074707</v>
+        <v>0.0001042972465977096</v>
       </c>
       <c r="F2" t="n">
-        <v>5.279055776464235</v>
+        <v>9.505808433179217e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>2.664535259100376e-15</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>-0.1099770941905521</v>
-      </c>
-      <c r="K2" t="n">
-        <v>-0.1465176493074707</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-5.279055776464235</v>
-      </c>
-      <c r="M2" t="n">
-        <v>-43.95529479224122</v>
-      </c>
-      <c r="N2" t="n">
-        <v>32.99312825716563</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
+        <v>-0.000569315001876651</v>
       </c>
     </row>
     <row r="3">
@@ -895,46 +805,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>0.05084079875519081</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>0.05332882759397755</v>
       </c>
       <c r="D3" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>-0.0007621265458027756</v>
       </c>
       <c r="E3" t="n">
-        <v>-5.000000000000002</v>
+        <v>-0.0007418827691351947</v>
       </c>
       <c r="F3" t="n">
-        <v>11.56576802356741</v>
+        <v>0.0003182918188883237</v>
       </c>
       <c r="G3" t="n">
-        <v>375</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>-4.440892098500626e-16</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1.77635683940025e-15</v>
-      </c>
-      <c r="L3" t="n">
-        <v>-11.56576802356741</v>
-      </c>
-      <c r="M3" t="n">
-        <v>375.0000000000002</v>
-      </c>
-      <c r="N3" t="n">
-        <v>9.947598300641403e-14</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
+        <v>-0.000569315001876651</v>
       </c>
     </row>
     <row r="4">
@@ -942,46 +828,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>0.1430712489045995</v>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>-1.326507896862112</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1099770941904298</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-4.85348235069253</v>
+        <v>-0.00498285583779166</v>
       </c>
       <c r="F4" t="n">
-        <v>1.844823800031678</v>
+        <v>-0.0003074486081795761</v>
       </c>
       <c r="G4" t="n">
-        <v>-456.0447052077589</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-5.087550610739213</v>
-      </c>
-      <c r="I4" t="n">
-        <v>-14.65176493074691</v>
-      </c>
-      <c r="J4" t="n">
-        <v>-0.1099770941904298</v>
-      </c>
-      <c r="K4" t="n">
-        <v>4.85348235069253</v>
-      </c>
-      <c r="L4" t="n">
-        <v>-6.844823800031678</v>
-      </c>
-      <c r="M4" t="n">
-        <v>-412.9200547985768</v>
-      </c>
-      <c r="N4" t="n">
-        <v>5.087550610739213</v>
-      </c>
-      <c r="O4" t="n">
-        <v>36.64718376883285</v>
+        <v>-0.0004752950001285505</v>
       </c>
     </row>
     <row r="5">
@@ -989,46 +851,45 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>0.05083666645072668</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>-0.0004686725354175329</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1099770941904126</v>
+        <v>-0.001708667026644057</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1465176493074694</v>
+        <v>-0.001606505297575576</v>
       </c>
       <c r="F5" t="n">
-        <v>-4.720944223535734</v>
+        <v>-0.0003074486081795765</v>
       </c>
       <c r="G5" t="n">
-        <v>43.95529479224121</v>
-      </c>
-      <c r="H5" t="n">
-        <v>217.0068717428343</v>
-      </c>
-      <c r="I5" t="n">
-        <v>-1.4210854715202e-14</v>
-      </c>
-      <c r="J5" t="n">
-        <v>-0.1099770941904126</v>
-      </c>
-      <c r="K5" t="n">
-        <v>-0.1465176493074694</v>
-      </c>
-      <c r="L5" t="n">
-        <v>-5.279055776464266</v>
-      </c>
-      <c r="M5" t="n">
-        <v>-43.95529479224121</v>
-      </c>
-      <c r="N5" t="n">
-        <v>-244.9124493892609</v>
-      </c>
-      <c r="O5" t="n">
-        <v>14.65176493074691</v>
+        <v>-0.0004752950001285505</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1037,6 +898,1516 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:V21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="21" customWidth="1" min="16" max="16"/>
+    <col width="21" customWidth="1" min="17" max="17"/>
+    <col width="21" customWidth="1" min="18" max="18"/>
+    <col width="21" customWidth="1" min="19" max="19"/>
+    <col width="21" customWidth="1" min="20" max="20"/>
+    <col width="20" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="22" max="22"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>DOF_global_fila</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>K_dof_3</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>K_dof_4</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>K_dof_5</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>K_dof_6</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>K_dof_7</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>K_dof_8</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>K_dof_9</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>K_dof_10</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>K_dof_11</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>K_dof_12</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>K_dof_13</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>K_dof_15</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>K_dof_16</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>K_dof_17</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>K_dof_18</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>K_dof_19</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>K_dof_20</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>K_dof_21</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>K_dof_22</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>K_dof_23</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Fl</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>222133.3333333333</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1110.666666666667</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>111066.6666666667</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>222133.3333333333</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-1110.666666666667</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>111066.6666666667</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>36232.53333333333</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-36232.53333333333</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-1110.666666666667</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>20007.40444444444</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-1110.666666666667</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-20000</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1110.666666666667</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>207.3244444444445</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1110.666666666667</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>9996</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-199.92</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>9996</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>6866.586666666667</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-9996</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>-199.92</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-9996</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>9</v>
+      </c>
+      <c r="B8" t="n">
+        <v>111066.6666666667</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1110.666666666667</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>330830.9333333333</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>-108697.6</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>10</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>111066.6666666667</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-1110.666666666667</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-9996</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>888533.3333333334</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>9996</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>333200</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>11</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-36232.53333333333</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>9996</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>702632.5333333333</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-9996</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>333200</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>12</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>7.404444444444445</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1110.666666666667</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-7.404444444444445</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1110.666666666667</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>13</v>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>7.404444444444445</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-1110.666666666667</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-7.404444444444445</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-1110.666666666667</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>-2.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>15</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-1110.666666666667</v>
+      </c>
+      <c r="M13" t="n">
+        <v>222133.3333333333</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1110.666666666667</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>111066.6666666667</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>187.5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>16</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1110.666666666667</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>222133.3333333333</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-1110.666666666667</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>111066.6666666667</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>17</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>36232.53333333333</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>-36232.53333333333</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>18</v>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-20000</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-7.404444444444445</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-1110.666666666667</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>20032.39444444445</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-1110.666666666667</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2499</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>19</v>
+      </c>
+      <c r="B17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-199.92</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-9996</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-7.404444444444445</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1110.666666666667</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>10207.32444444444</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1110.666666666667</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>-9996</v>
+      </c>
+      <c r="V17" t="n">
+        <v>-2.5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>20</v>
+      </c>
+      <c r="B18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-199.92</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>9996</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6891.576666666667</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-2499</v>
+      </c>
+      <c r="T18" t="n">
+        <v>9996</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>-7.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>21</v>
+      </c>
+      <c r="B19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-108697.6</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-1110.666666666667</v>
+      </c>
+      <c r="M19" t="n">
+        <v>111066.6666666667</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1110.666666666667</v>
+      </c>
+      <c r="R19" t="n">
+        <v>-2499</v>
+      </c>
+      <c r="S19" t="n">
+        <v>664030.9333333333</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>-62.5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>22</v>
+      </c>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-9996</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>333200</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1110.666666666667</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>111066.6666666667</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>-1110.666666666667</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>9996</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>942882.1333333333</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>-125</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>23</v>
+      </c>
+      <c r="B21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>9996</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>333200</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>-36232.53333333333</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2499</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-9996</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1035832.533333333</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1332,7 +2703,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1628,7 +2999,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1795,315 +3166,6 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:S4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
-    <col width="18" customWidth="1" min="18" max="18"/>
-    <col width="18" customWidth="1" min="19" max="19"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Carga ID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Barra ID</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Nodo Inicial</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Nodo Final</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>f_local_x</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>f_local_y</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>f_local_z</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Reacc_i_Fx_local</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Reacc_i_Fy_local</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Reacc_i_Fz_local</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Reacc_i_Mx_local</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Reacc_i_My_local</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Reacc_i_Mz_local</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Reacc_f_Fx_local</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Reacc_f_Fy_local</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Reacc_f_Fz_local</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Reacc_f_Mx_local</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Reacc_f_My_local</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Reacc_f_Mz_local</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-5</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>187.5</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>-187.5</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="n">
-        <v>3</v>
-      </c>
-      <c r="C3" t="n">
-        <v>4</v>
-      </c>
-      <c r="D3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>-125</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>125</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="n">
-        <v>4</v>
-      </c>
-      <c r="C4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>-10</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>5</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>-125</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>125</v>
-      </c>
-      <c r="S4" t="n">
         <v>0</v>
       </c>
     </row>

--- a/supertesteo_resultados.xlsx
+++ b/supertesteo_resultados.xlsx
@@ -8,13 +8,14 @@
   </bookViews>
   <sheets>
     <sheet name="reacciones_de_estructura_Globales" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Desplazamientos_globales_D" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sistema_reducido_Kll_Fl" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Cargas_Globales_en_nudos" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="reacciones_locales_de_empotramiento" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Vector_Nodal_Equivalente" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Ejes_Locales" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Matriz_Rotacion_T" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="F_interna_Locales" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Desplazamientos_globales_D" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sistema_reducido_Kll_Fl" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Cargas_Globales_en_nudos" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="reacciones_locales_de_empotramiento" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Vector_Nodal_Equivalente" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Ejes_Locales" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Matriz_Rotacion_T" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -728,6 +729,302 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:O5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Barra ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Nodo Inicial</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Nodo Final</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Fx_i</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Fy_i</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Fz_i</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Mx_i</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>My_i</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Mz_i</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Fx_f</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Fy_f</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Fz_f</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Mx_f</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>My_f</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Mz_f</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5.080843638685171</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.3132746458246708</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-0.08264608928248485</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>3.552713678800501e-15</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-5.080843638685171</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-0.3132746458246708</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.08264608928248485</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>24.79382678474544</v>
+      </c>
+      <c r="O2" t="n">
+        <v>93.98239374740125</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>11.39111351096038</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2.664535259100376e-15</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2.220446049250313e-16</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-2.273736754432321e-13</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-11.39111351096038</v>
+      </c>
+      <c r="K3" t="n">
+        <v>4.999999999999997</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-2.220446049250313e-16</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>-4.263256414560601e-14</v>
+      </c>
+      <c r="O3" t="n">
+        <v>-749.9999999999998</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4.686725354175329</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.08264608928241235</v>
+      </c>
+      <c r="F4" t="n">
+        <v>6.471957149645529</v>
+      </c>
+      <c r="G4" t="n">
+        <v>16.70946291623017</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-656.0176062525985</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-31.32746458246704</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-4.686725354175329</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-0.08264608928241235</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-1.471957149645529</v>
+      </c>
+      <c r="M4" t="n">
+        <v>-16.70946291623017</v>
+      </c>
+      <c r="N4" t="n">
+        <v>-138.3738236765075</v>
+      </c>
+      <c r="O4" t="n">
+        <v>47.85668243894946</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.08264608928243433</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.3132746458246718</v>
+      </c>
+      <c r="F5" t="n">
+        <v>5.080843638685151</v>
+      </c>
+      <c r="G5" t="n">
+        <v>93.98239374740122</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-24.79382678474538</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-0.08264608928243433</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-0.3132746458246718</v>
+      </c>
+      <c r="L5" t="n">
+        <v>4.919156361314849</v>
+      </c>
+      <c r="M5" t="n">
+        <v>-93.98239374740122</v>
+      </c>
+      <c r="N5" t="n">
+        <v>16.70946291623029</v>
+      </c>
+      <c r="O5" t="n">
+        <v>31.32746458246709</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -897,7 +1194,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2407,7 +2704,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2703,7 +3000,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2999,7 +3296,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3174,7 +3471,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3452,7 +3749,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/supertesteo_resultados.xlsx
+++ b/supertesteo_resultados.xlsx
@@ -25,16 +25,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -45,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -53,21 +50,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -454,77 +442,77 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Barra ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Nodo Inicial</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Nodo Final</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Fx_i</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Fy_i</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Fz_i</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Mx_i</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>My_i</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Mz_i</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Fx_f</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Fy_f</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Fz_f</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Mx_f</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>My_f</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Mz_f</t>
         </is>
@@ -750,77 +738,77 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Barra ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Nodo Inicial</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Nodo Final</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Fx_i</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Fy_i</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Fz_i</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Mx_i</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>My_i</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Mz_i</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Fx_f</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Fy_f</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Fz_f</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Mx_f</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>My_f</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Mz_f</t>
         </is>
@@ -1038,37 +1026,37 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Nodo ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Ux</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Uy</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Uz</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Rx</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Ry</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Rz</t>
         </is>
@@ -1228,112 +1216,112 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>DOF_global_fila</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>K_dof_3</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>K_dof_4</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>K_dof_5</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>K_dof_6</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>K_dof_7</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>K_dof_8</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>K_dof_9</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>K_dof_10</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>K_dof_11</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>K_dof_12</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>K_dof_13</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>K_dof_15</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>K_dof_16</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>K_dof_17</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>K_dof_18</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>K_dof_19</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>K_dof_20</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>K_dof_21</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>K_dof_22</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>K_dof_23</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Fl</t>
         </is>
@@ -2731,77 +2719,77 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Barra ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Nodo Inicial</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Nodo Final</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Fx_i</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Fy_i</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Fz_i</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Mx_i</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>My_i</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Mz_i</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Fx_f</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Fy_f</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Fz_f</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Mx_f</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>My_f</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Mz_f</t>
         </is>
@@ -3027,77 +3015,77 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Barra ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Nodo Inicial</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Nodo Final</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Fx_i</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Fy_i</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Fz_i</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Mx_i</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>My_i</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Mz_i</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Fx_f</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Fy_f</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Fz_f</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Mx_f</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>My_f</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Mz_f</t>
         </is>
@@ -3315,37 +3303,37 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Nodo ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Fx</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Fy</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Fz</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Mx</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>My</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Mz</t>
         </is>
@@ -3497,72 +3485,72 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Barra ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Nodo Inicial</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Nodo Final</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Longitud (cm)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>tita (deg)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>x_local_x</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>x_local_y</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>x_local_z</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>y_local_x</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>y_local_y</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>y_local_z</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>z_local_x</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>z_local_y</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>z_local_z</t>
         </is>
@@ -3777,82 +3765,82 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Barra ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Nodo Inicial</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Nodo Final</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Fila</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>C2</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>C3</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>C4</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>C5</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>C6</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>C7</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>C8</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>C9</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>C10</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>C11</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>C12</t>
         </is>

--- a/supertesteo_resultados.xlsx
+++ b/supertesteo_resultados.xlsx
@@ -7,15 +7,21 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="reacciones_de_estructura_Globales" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="F_interna_Locales" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Desplazamientos_globales_D" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Sistema_reducido_Kll_Fl" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Cargas_Globales_en_nudos" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="reacciones_locales_de_empotramiento" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Vector_Nodal_Equivalente" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Ejes_Locales" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Resumen_Barras" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Ternas_locales_en_Ejes_globales" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="K_locales" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="F_locales_de_cargas" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="R_locales_de_empotramiento_cargas" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Cargas_nodales_locales" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cargas_Nodales_Aplicadas" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Matriz_R_2D" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Matriz_Rotacion_T" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Cargas_nodales_equivalentes_Globales" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Vector_Nodal_Equivalente" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Sistema_reducido_Kll_Fl" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Desplazamientos_globales_D" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Solicitacion_extremo_de_barra_Globales" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Solicitacion_extremo_de_barra_Locales" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,13 +31,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -42,7 +51,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -50,12 +59,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -421,100 +439,124 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
-    <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
-    <col width="21" customWidth="1" min="12" max="12"/>
-    <col width="21" customWidth="1" min="13" max="13"/>
-    <col width="24" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="19" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="9" customWidth="1" min="15" max="15"/>
+    <col width="5" customWidth="1" min="16" max="16"/>
+    <col width="17" customWidth="1" min="17" max="17"/>
+    <col width="8" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Barra ID</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Nodo Inicial</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Nodo Final</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Fx_i</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Fy_i</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Fz_i</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Mx_i</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>My_i</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Mz_i</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Fx_f</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Fy_f</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Fz_f</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Mx_f</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>My_f</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>Mz_f</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Ubicación i - X</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Ubicación i - Y</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Ubicación i - Z</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Ubicación f - X</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Ubicación f - Y</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Ubicación f - Z</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Restricciones i</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Restricciones f</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Longitud (cm)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Área A (cm2)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Inercia I_y (cm4)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Inercia I_z (cm4)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Peso específico</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Material</t>
         </is>
       </c>
     </row>
@@ -523,46 +565,60 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>200</v>
       </c>
       <c r="D2" t="n">
-        <v>0.08264608928248485</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3132746458246708</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>5.080843638685171</v>
+        <v>200</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>3.552713678800501e-15</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
+        <v>300</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Ux,Uy,Uz</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
       </c>
       <c r="J2" t="n">
-        <v>-0.08264608928248485</v>
+        <v>300</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.3132746458246708</v>
+        <v>100</v>
       </c>
       <c r="L2" t="n">
-        <v>-5.080843638685171</v>
+        <v>833</v>
       </c>
       <c r="M2" t="n">
-        <v>-93.98239374740125</v>
+        <v>833</v>
       </c>
       <c r="N2" t="n">
-        <v>24.79382678474544</v>
+        <v>7720</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>20000</v>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="n">
+        <v>1408</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -570,46 +626,60 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>200</v>
       </c>
       <c r="D3" t="n">
-        <v>-2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>2.664535259100376e-15</v>
+        <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>11.39111351096038</v>
+        <v>200</v>
       </c>
       <c r="G3" t="n">
-        <v>2.273736754432321e-13</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
+        <v>300</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Uz</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
       </c>
       <c r="J3" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>300</v>
       </c>
       <c r="K3" t="n">
-        <v>4.999999999999997</v>
+        <v>100</v>
       </c>
       <c r="L3" t="n">
-        <v>-11.39111351096038</v>
+        <v>833</v>
       </c>
       <c r="M3" t="n">
-        <v>749.9999999999998</v>
+        <v>833</v>
       </c>
       <c r="N3" t="n">
-        <v>-4.263256414560601e-14</v>
+        <v>7720</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>20000</v>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="n">
+        <v>1408</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -617,46 +687,60 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>200</v>
       </c>
       <c r="D4" t="n">
-        <v>0.08264608928241235</v>
+        <v>300</v>
       </c>
       <c r="E4" t="n">
-        <v>-4.686725354175329</v>
+        <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>6.471957149645529</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-656.0176062525985</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-16.70946291623017</v>
-      </c>
-      <c r="I4" t="n">
-        <v>-31.32746458246704</v>
+        <v>300</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Ux,Uy,Uz,Rx,Ry,Rz</t>
+        </is>
       </c>
       <c r="J4" t="n">
-        <v>-0.08264608928241235</v>
+        <v>200</v>
       </c>
       <c r="K4" t="n">
-        <v>4.686725354175329</v>
+        <v>100</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.471957149645529</v>
+        <v>833</v>
       </c>
       <c r="M4" t="n">
-        <v>-138.3738236765075</v>
+        <v>833</v>
       </c>
       <c r="N4" t="n">
-        <v>16.70946291623017</v>
+        <v>7720</v>
       </c>
       <c r="O4" t="n">
-        <v>47.85668243894946</v>
+        <v>20000</v>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="n">
+        <v>1408</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -664,46 +748,60 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>200</v>
       </c>
       <c r="D5" t="n">
-        <v>0.08264608928243433</v>
+        <v>300</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3132746458246718</v>
+        <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>5.080843638685151</v>
+        <v>200</v>
       </c>
       <c r="G5" t="n">
-        <v>93.98239374740122</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-24.79382678474538</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
+        <v>300</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
       </c>
       <c r="J5" t="n">
-        <v>-0.08264608928243433</v>
+        <v>100</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.3132746458246718</v>
+        <v>100</v>
       </c>
       <c r="L5" t="n">
-        <v>4.919156361314849</v>
+        <v>833</v>
       </c>
       <c r="M5" t="n">
-        <v>-93.98239374740122</v>
+        <v>833</v>
       </c>
       <c r="N5" t="n">
-        <v>16.70946291623029</v>
+        <v>7720</v>
       </c>
       <c r="O5" t="n">
-        <v>31.32746458246709</v>
+        <v>20000</v>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="n">
+        <v>1408</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -711,7 +809,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -723,92 +821,92 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
-    <col width="25" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
-    <col width="21" customWidth="1" min="13" max="13"/>
-    <col width="24" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="6" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="6" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Barra ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Nodo Inicial</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Nodo Final</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Fx_i</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Fy_i</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Fz_i</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Mx_i</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>My_i</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Mz_i</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Fx_f</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Fy_f</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Fz_f</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Mx_f</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>My_f</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Mz_f</t>
         </is>
@@ -825,40 +923,40 @@
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>5.080843638685171</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3132746458246708</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.08264608928248485</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>3.552713678800501e-15</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-5.080843638685171</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.3132746458246708</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08264608928248485</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>24.79382678474544</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>93.98239374740125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -872,40 +970,40 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>11.39111351096038</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>2.664535259100376e-15</v>
+        <v>-2.5</v>
       </c>
       <c r="F3" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>187.5</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.273736754432321e-13</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-11.39111351096038</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>4.999999999999997</v>
+        <v>-2.5</v>
       </c>
       <c r="L3" t="n">
-        <v>-2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>-187.5</v>
       </c>
       <c r="N3" t="n">
-        <v>-4.263256414560601e-14</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-749.9999999999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -919,40 +1017,40 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>4.686725354175329</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.08264608928241235</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>6.471957149645529</v>
+        <v>-2.5</v>
       </c>
       <c r="G4" t="n">
-        <v>16.70946291623017</v>
+        <v>125</v>
       </c>
       <c r="H4" t="n">
-        <v>-656.0176062525985</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>-31.32746458246704</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-4.686725354175329</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.08264608928241235</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.471957149645529</v>
+        <v>-2.5</v>
       </c>
       <c r="M4" t="n">
-        <v>-16.70946291623017</v>
+        <v>-125</v>
       </c>
       <c r="N4" t="n">
-        <v>-138.3738236765075</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>47.85668243894946</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -966,40 +1064,40 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>0.08264608928243433</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3132746458246718</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>5.080843638685151</v>
+        <v>-5</v>
       </c>
       <c r="G5" t="n">
-        <v>93.98239374740122</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>-24.79382678474538</v>
+        <v>125</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.08264608928243433</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.3132746458246718</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>4.919156361314849</v>
+        <v>-5</v>
       </c>
       <c r="M5" t="n">
-        <v>-93.98239374740122</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>16.70946291623029</v>
+        <v>-125</v>
       </c>
       <c r="O5" t="n">
-        <v>31.32746458246709</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1007,58 +1105,64 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="5" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Nodo ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Ux</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Uy</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Uz</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Rx</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Ry</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Rz</t>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Origen</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Fx</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Fy</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Fz</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Mx</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>My</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Mz</t>
         </is>
       </c>
     </row>
@@ -1066,8 +1170,10 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="n">
-        <v>0</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -1076,104 +1182,407 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0001042972465977096</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>9.505808433179217e-05</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.000569315001876651</v>
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="n">
-        <v>0.05084079875519081</v>
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ↳ aporte cargas nodales</t>
+        </is>
       </c>
       <c r="C3" t="n">
-        <v>0.05332882759397755</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0007621265458027756</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0007418827691351947</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0003182918188883237</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.000569315001876651</v>
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0.1430712489045995</v>
+        <v>1</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ↳ aporte cargas en barras (equiv.)</t>
+        </is>
       </c>
       <c r="C4" t="n">
-        <v>-1.326507896862112</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.00498285583779166</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0003074486081795761</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.0004752950001285505</v>
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="n">
-        <v>0.05083666645072668</v>
+        <v>2</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
       </c>
       <c r="C5" t="n">
-        <v>-0.0004686725354175329</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.001708667026644057</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.001606505297575576</v>
+        <v>-5</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0003074486081795765</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.0004752950001285505</v>
+        <v>125</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ↳ aporte cargas nodales</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ↳ aporte cargas en barras (equiv.)</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>125</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>187.5</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ↳ aporte cargas nodales</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ↳ aporte cargas en barras (equiv.)</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>187.5</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-62.5</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-125</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>4</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ↳ aporte cargas nodales</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ↳ aporte cargas en barras (equiv.)</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-62.5</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-125</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-125</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>5</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ↳ aporte cargas nodales</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>5</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ↳ aporte cargas en barras (equiv.)</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-125</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1182,7 +1591,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1216,112 +1625,112 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>DOF_global_fila</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>K_dof_3</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>K_dof_4</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>K_dof_5</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>K_dof_6</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>K_dof_7</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>K_dof_8</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>K_dof_9</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>K_dof_10</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>K_dof_11</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>K_dof_12</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>K_dof_13</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>K_dof_15</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>K_dof_16</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>K_dof_17</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>K_dof_18</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>K_dof_19</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>K_dof_20</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>K_dof_21</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>K_dof_22</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>K_dof_23</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Fl</t>
         </is>
@@ -2685,6 +3094,3676 @@
       </c>
       <c r="V21" t="n">
         <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Nodo ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Ux</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Uy</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Uz</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Rx</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Ry</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Rz</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.0001042972465977096</v>
+      </c>
+      <c r="F2" t="n">
+        <v>9.505808433179217e-05</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-0.000569315001876651</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.05084079875519081</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.05332882759397755</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.0007621265458027756</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-0.0007418827691351947</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.0003182918188883237</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-0.000569315001876651</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.1430712489045995</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-1.326507896862112</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-0.00498285583779166</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-0.0003074486081795761</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-0.0004752950001285505</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.05083666645072668</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.0004686725354175329</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.001708667026644057</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.001606505297575576</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-0.0003074486081795765</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-0.0004752950001285505</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="23" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Barra ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Nodo Inicial</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Nodo Final</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Fx_i</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Fy_i</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Fz_i</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Mx_i</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>My_i</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Mz_i</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Fx_f</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Fy_f</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Fz_f</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Mx_f</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>My_f</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Mz_f</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.08264608928248485</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.3132746458246708</v>
+      </c>
+      <c r="F2" t="n">
+        <v>5.080843638685171</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>3.552713678800501e-15</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-0.08264608928248485</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-0.3132746458246708</v>
+      </c>
+      <c r="L2" t="n">
+        <v>-5.080843638685171</v>
+      </c>
+      <c r="M2" t="n">
+        <v>-93.98239374740125</v>
+      </c>
+      <c r="N2" t="n">
+        <v>24.79382678474544</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-2.220446049250313e-16</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2.664535259100376e-15</v>
+      </c>
+      <c r="F3" t="n">
+        <v>11.39111351096038</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2.273736754432321e-13</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2.220446049250313e-16</v>
+      </c>
+      <c r="K3" t="n">
+        <v>4.999999999999997</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-11.39111351096038</v>
+      </c>
+      <c r="M3" t="n">
+        <v>749.9999999999998</v>
+      </c>
+      <c r="N3" t="n">
+        <v>-4.263256414560601e-14</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.08264608928241235</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-4.686725354175329</v>
+      </c>
+      <c r="F4" t="n">
+        <v>6.471957149645529</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-656.0176062525985</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-16.70946291623017</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-31.32746458246704</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-0.08264608928241235</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4.686725354175329</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-1.471957149645529</v>
+      </c>
+      <c r="M4" t="n">
+        <v>-138.3738236765075</v>
+      </c>
+      <c r="N4" t="n">
+        <v>16.70946291623017</v>
+      </c>
+      <c r="O4" t="n">
+        <v>47.85668243894946</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.08264608928243433</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.3132746458246718</v>
+      </c>
+      <c r="F5" t="n">
+        <v>5.080843638685151</v>
+      </c>
+      <c r="G5" t="n">
+        <v>93.98239374740122</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-24.79382678474538</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-0.08264608928243433</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-0.3132746458246718</v>
+      </c>
+      <c r="L5" t="n">
+        <v>4.919156361314849</v>
+      </c>
+      <c r="M5" t="n">
+        <v>-93.98239374740122</v>
+      </c>
+      <c r="N5" t="n">
+        <v>16.70946291623029</v>
+      </c>
+      <c r="O5" t="n">
+        <v>31.32746458246709</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Barra ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Nodo Inicial</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Nodo Final</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Fx_i</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Fy_i</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Fz_i</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Mx_i</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>My_i</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Mz_i</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Fx_f</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Fy_f</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Fz_f</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Mx_f</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>My_f</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Mz_f</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5.080843638685171</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.3132746458246708</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-0.08264608928248485</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>3.552713678800501e-15</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-5.080843638685171</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-0.3132746458246708</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.08264608928248485</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>24.79382678474544</v>
+      </c>
+      <c r="O2" t="n">
+        <v>93.98239374740125</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>11.39111351096038</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2.664535259100376e-15</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2.220446049250313e-16</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-2.273736754432321e-13</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-11.39111351096038</v>
+      </c>
+      <c r="K3" t="n">
+        <v>4.999999999999997</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-2.220446049250313e-16</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>-4.263256414560601e-14</v>
+      </c>
+      <c r="O3" t="n">
+        <v>-749.9999999999998</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4.686725354175329</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.08264608928241235</v>
+      </c>
+      <c r="F4" t="n">
+        <v>6.471957149645529</v>
+      </c>
+      <c r="G4" t="n">
+        <v>16.70946291623017</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-656.0176062525985</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-31.32746458246704</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-4.686725354175329</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-0.08264608928241235</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-1.471957149645529</v>
+      </c>
+      <c r="M4" t="n">
+        <v>-16.70946291623017</v>
+      </c>
+      <c r="N4" t="n">
+        <v>-138.3738236765075</v>
+      </c>
+      <c r="O4" t="n">
+        <v>47.85668243894946</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.08264608928243433</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.3132746458246718</v>
+      </c>
+      <c r="F5" t="n">
+        <v>5.080843638685151</v>
+      </c>
+      <c r="G5" t="n">
+        <v>93.98239374740122</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-24.79382678474538</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-0.08264608928243433</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-0.3132746458246718</v>
+      </c>
+      <c r="L5" t="n">
+        <v>4.919156361314849</v>
+      </c>
+      <c r="M5" t="n">
+        <v>-93.98239374740122</v>
+      </c>
+      <c r="N5" t="n">
+        <v>16.70946291623029</v>
+      </c>
+      <c r="O5" t="n">
+        <v>31.32746458246709</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Barra ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Nodo Inicial</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Nodo Final</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>tita (deg)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>x_local_x</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>x_local_y</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>x_local_z</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>y_local_x</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>y_local_y</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>y_local_z</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>z_local_x</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>z_local_y</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>z_local_z</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P49"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="21" customWidth="1" min="15" max="15"/>
+    <col width="21" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Barra ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Nodo Inicial</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Nodo Final</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Fila</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>C8</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>C11</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>C12</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>6666.666666666667</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-6666.666666666667</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>7.404444444444445</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1110.666666666667</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-7.404444444444445</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1110.666666666667</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>7.404444444444445</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-1110.666666666667</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>-7.404444444444445</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-1110.666666666667</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>36232.53333333333</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-36232.53333333333</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-1110.666666666667</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>222133.3333333333</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1110.666666666667</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>111066.6666666667</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1110.666666666667</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>222133.3333333333</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-1110.666666666667</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>111066.6666666667</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-6666.666666666667</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>6666.666666666667</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="n">
+        <v>8</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-7.404444444444445</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-1110.666666666667</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>7.404444444444445</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-1110.666666666667</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="n">
+        <v>9</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-7.404444444444445</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1110.666666666667</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>7.404444444444445</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1110.666666666667</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1</v>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-36232.53333333333</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>36232.53333333333</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="n">
+        <v>11</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-1110.666666666667</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>111066.6666666667</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1110.666666666667</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>222133.3333333333</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="n">
+        <v>12</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1110.666666666667</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>111066.6666666667</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-1110.666666666667</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>222133.3333333333</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>6666.666666666667</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-6666.666666666667</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2</v>
+      </c>
+      <c r="B15" t="n">
+        <v>3</v>
+      </c>
+      <c r="C15" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>7.404444444444445</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1110.666666666667</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-7.404444444444445</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1110.666666666667</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2</v>
+      </c>
+      <c r="B16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" t="n">
+        <v>4</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>7.404444444444445</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-1110.666666666667</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>-7.404444444444445</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>-1110.666666666667</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B17" t="n">
+        <v>3</v>
+      </c>
+      <c r="C17" t="n">
+        <v>4</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>36232.53333333333</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-36232.53333333333</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" t="n">
+        <v>3</v>
+      </c>
+      <c r="C18" t="n">
+        <v>4</v>
+      </c>
+      <c r="D18" t="n">
+        <v>5</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-1110.666666666667</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>222133.3333333333</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1110.666666666667</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>111066.6666666667</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D19" t="n">
+        <v>6</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1110.666666666667</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>222133.3333333333</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-1110.666666666667</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>111066.6666666667</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" t="n">
+        <v>3</v>
+      </c>
+      <c r="C20" t="n">
+        <v>4</v>
+      </c>
+      <c r="D20" t="n">
+        <v>7</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-6666.666666666667</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>6666.666666666667</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" t="n">
+        <v>3</v>
+      </c>
+      <c r="C21" t="n">
+        <v>4</v>
+      </c>
+      <c r="D21" t="n">
+        <v>8</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-7.404444444444445</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-1110.666666666667</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>7.404444444444445</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>-1110.666666666667</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" t="n">
+        <v>3</v>
+      </c>
+      <c r="C22" t="n">
+        <v>4</v>
+      </c>
+      <c r="D22" t="n">
+        <v>9</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-7.404444444444445</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1110.666666666667</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>7.404444444444445</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1110.666666666667</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" t="n">
+        <v>3</v>
+      </c>
+      <c r="C23" t="n">
+        <v>4</v>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-36232.53333333333</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>36232.53333333333</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" t="n">
+        <v>3</v>
+      </c>
+      <c r="C24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D24" t="n">
+        <v>11</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-1110.666666666667</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>111066.6666666667</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1110.666666666667</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>222133.3333333333</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2</v>
+      </c>
+      <c r="B25" t="n">
+        <v>3</v>
+      </c>
+      <c r="C25" t="n">
+        <v>4</v>
+      </c>
+      <c r="D25" t="n">
+        <v>12</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1110.666666666667</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>111066.6666666667</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-1110.666666666667</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>222133.3333333333</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>3</v>
+      </c>
+      <c r="B26" t="n">
+        <v>4</v>
+      </c>
+      <c r="C26" t="n">
+        <v>5</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-10000</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B27" t="n">
+        <v>4</v>
+      </c>
+      <c r="C27" t="n">
+        <v>5</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>24.99</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2499</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-24.99</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2499</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>3</v>
+      </c>
+      <c r="B28" t="n">
+        <v>4</v>
+      </c>
+      <c r="C28" t="n">
+        <v>5</v>
+      </c>
+      <c r="D28" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>24.99</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>-2499</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>-24.99</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>-2499</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>3</v>
+      </c>
+      <c r="B29" t="n">
+        <v>4</v>
+      </c>
+      <c r="C29" t="n">
+        <v>5</v>
+      </c>
+      <c r="D29" t="n">
+        <v>4</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>54348.8</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>-54348.8</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>3</v>
+      </c>
+      <c r="B30" t="n">
+        <v>4</v>
+      </c>
+      <c r="C30" t="n">
+        <v>5</v>
+      </c>
+      <c r="D30" t="n">
+        <v>5</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-2499</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>333200</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>2499</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>166600</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>3</v>
+      </c>
+      <c r="B31" t="n">
+        <v>4</v>
+      </c>
+      <c r="C31" t="n">
+        <v>5</v>
+      </c>
+      <c r="D31" t="n">
+        <v>6</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2499</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>333200</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>-2499</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>166600</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>3</v>
+      </c>
+      <c r="B32" t="n">
+        <v>4</v>
+      </c>
+      <c r="C32" t="n">
+        <v>5</v>
+      </c>
+      <c r="D32" t="n">
+        <v>7</v>
+      </c>
+      <c r="E32" t="n">
+        <v>-10000</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>3</v>
+      </c>
+      <c r="B33" t="n">
+        <v>4</v>
+      </c>
+      <c r="C33" t="n">
+        <v>5</v>
+      </c>
+      <c r="D33" t="n">
+        <v>8</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>-24.99</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>-2499</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>24.99</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>-2499</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>3</v>
+      </c>
+      <c r="B34" t="n">
+        <v>4</v>
+      </c>
+      <c r="C34" t="n">
+        <v>5</v>
+      </c>
+      <c r="D34" t="n">
+        <v>9</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-24.99</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>2499</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>24.99</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>2499</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>3</v>
+      </c>
+      <c r="B35" t="n">
+        <v>4</v>
+      </c>
+      <c r="C35" t="n">
+        <v>5</v>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>-54348.8</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>54348.8</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>3</v>
+      </c>
+      <c r="B36" t="n">
+        <v>4</v>
+      </c>
+      <c r="C36" t="n">
+        <v>5</v>
+      </c>
+      <c r="D36" t="n">
+        <v>11</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-2499</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>166600</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>2499</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>333200</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>3</v>
+      </c>
+      <c r="B37" t="n">
+        <v>4</v>
+      </c>
+      <c r="C37" t="n">
+        <v>5</v>
+      </c>
+      <c r="D37" t="n">
+        <v>12</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2499</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>166600</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>-2499</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>333200</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>4</v>
+      </c>
+      <c r="B38" t="n">
+        <v>2</v>
+      </c>
+      <c r="C38" t="n">
+        <v>4</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>-20000</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>4</v>
+      </c>
+      <c r="B39" t="n">
+        <v>2</v>
+      </c>
+      <c r="C39" t="n">
+        <v>4</v>
+      </c>
+      <c r="D39" t="n">
+        <v>2</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>199.92</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>9996</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>-199.92</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>9996</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>4</v>
+      </c>
+      <c r="B40" t="n">
+        <v>2</v>
+      </c>
+      <c r="C40" t="n">
+        <v>4</v>
+      </c>
+      <c r="D40" t="n">
+        <v>3</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>199.92</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>-9996</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>-199.92</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>-9996</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>4</v>
+      </c>
+      <c r="B41" t="n">
+        <v>2</v>
+      </c>
+      <c r="C41" t="n">
+        <v>4</v>
+      </c>
+      <c r="D41" t="n">
+        <v>4</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>108697.6</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>-108697.6</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>4</v>
+      </c>
+      <c r="B42" t="n">
+        <v>2</v>
+      </c>
+      <c r="C42" t="n">
+        <v>4</v>
+      </c>
+      <c r="D42" t="n">
+        <v>5</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-9996</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>666400</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>9996</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>333200</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>4</v>
+      </c>
+      <c r="B43" t="n">
+        <v>2</v>
+      </c>
+      <c r="C43" t="n">
+        <v>4</v>
+      </c>
+      <c r="D43" t="n">
+        <v>6</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>9996</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>666400</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>-9996</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>333200</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>4</v>
+      </c>
+      <c r="B44" t="n">
+        <v>2</v>
+      </c>
+      <c r="C44" t="n">
+        <v>4</v>
+      </c>
+      <c r="D44" t="n">
+        <v>7</v>
+      </c>
+      <c r="E44" t="n">
+        <v>-20000</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>20000</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>4</v>
+      </c>
+      <c r="B45" t="n">
+        <v>2</v>
+      </c>
+      <c r="C45" t="n">
+        <v>4</v>
+      </c>
+      <c r="D45" t="n">
+        <v>8</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>-199.92</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>-9996</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>199.92</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>-9996</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>4</v>
+      </c>
+      <c r="B46" t="n">
+        <v>2</v>
+      </c>
+      <c r="C46" t="n">
+        <v>4</v>
+      </c>
+      <c r="D46" t="n">
+        <v>9</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
+        <v>-199.92</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>9996</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>199.92</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>9996</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>4</v>
+      </c>
+      <c r="B47" t="n">
+        <v>2</v>
+      </c>
+      <c r="C47" t="n">
+        <v>4</v>
+      </c>
+      <c r="D47" t="n">
+        <v>10</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>-108697.6</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>108697.6</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>4</v>
+      </c>
+      <c r="B48" t="n">
+        <v>2</v>
+      </c>
+      <c r="C48" t="n">
+        <v>4</v>
+      </c>
+      <c r="D48" t="n">
+        <v>11</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="n">
+        <v>-9996</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>333200</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>9996</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>666400</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>4</v>
+      </c>
+      <c r="B49" t="n">
+        <v>2</v>
+      </c>
+      <c r="C49" t="n">
+        <v>4</v>
+      </c>
+      <c r="D49" t="n">
+        <v>12</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="n">
+        <v>9996</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>333200</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>-9996</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>666400</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Carga ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Barra ID</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Nodo Inicial</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Nodo Final</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Fx_local</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Fy_local</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Fz_local</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-5</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-10</v>
       </c>
     </row>
   </sheetData>
@@ -2698,124 +6777,130 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:P4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="6" customWidth="1" min="5" max="5"/>
     <col width="6" customWidth="1" min="6" max="6"/>
-    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
     <col width="7" customWidth="1" min="8" max="8"/>
-    <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="10" max="10"/>
     <col width="6" customWidth="1" min="11" max="11"/>
     <col width="6" customWidth="1" min="12" max="12"/>
-    <col width="8" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
-    <col width="6" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
+    <col width="7" customWidth="1" min="14" max="14"/>
+    <col width="7" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Carga ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Barra ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Nodo Inicial</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Nodo Final</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Fx_i</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Fy_i</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Fz_i</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Mx_i</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>My_i</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Mz_i</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Fx_f</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Fy_f</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Fz_f</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Mx_f</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>My_f</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>Mz_f</t>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Rx_i</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Ry_i</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Rz_i</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>RMx_i</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>RMy_i</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>RMz_i</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Rx_f</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Ry_f</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Rz_f</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>RMx_f</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>RMy_f</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>RMz_f</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -2824,27 +6909,30 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>187.5</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>-0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>-187.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" t="n">
         <v>3</v>
@@ -2853,40 +6941,43 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.5</v>
+        <v>-0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G3" t="n">
-        <v>187.5</v>
+        <v>2.5</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>-125</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.5</v>
+        <v>-0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M3" t="n">
-        <v>-187.5</v>
+        <v>2.5</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>125</v>
+      </c>
+      <c r="P3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="4">
@@ -2897,90 +6988,46 @@
         <v>4</v>
       </c>
       <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="G4" t="n">
         <v>5</v>
       </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-125</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>5</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
         <v>125</v>
       </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="M4" t="n">
-        <v>-125</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C5" t="n">
-        <v>4</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>-5</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>125</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>-5</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>-125</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
+      <c r="P4" t="n">
+        <v>-0</v>
       </c>
     </row>
   </sheetData>
@@ -2994,153 +7041,162 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:P4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="6" customWidth="1" min="5" max="5"/>
     <col width="6" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
     <col width="7" customWidth="1" min="9" max="9"/>
-    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
     <col width="6" customWidth="1" min="11" max="11"/>
     <col width="6" customWidth="1" min="12" max="12"/>
     <col width="6" customWidth="1" min="13" max="13"/>
     <col width="7" customWidth="1" min="14" max="14"/>
     <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="7" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Carga ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Barra ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Nodo Inicial</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Nodo Final</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Fx_i</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Fy_i</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Fz_i</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Mx_i</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>My_i</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Mz_i</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Fx_f</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Fy_f</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Fz_f</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Mx_f</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>My_f</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>Mz_f</t>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Rx_i</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Ry_i</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Rz_i</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>RMx_i</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>RMy_i</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>RMz_i</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Rx_f</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Ry_f</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Rz_f</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>RMx_f</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>RMy_f</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>RMz_f</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>-2.5</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>-187.5</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>-2.5</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>187.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" t="n">
         <v>3</v>
@@ -3149,40 +7205,43 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>-2.5</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I3" t="n">
-        <v>187.5</v>
+        <v>125</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K3" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>-2.5</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O3" t="n">
-        <v>-187.5</v>
+        <v>-125</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -3193,89 +7252,45 @@
         <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="H4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>125</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="N4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O4" t="n">
         <v>-125</v>
       </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>125</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C5" t="n">
-        <v>4</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>5</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-125</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>5</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>125</v>
-      </c>
-      <c r="O5" t="n">
+      <c r="P4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3290,171 +7305,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="5" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="5" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Nodo ID</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Fx</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Fy</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Fz</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Mx</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>My</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Mz</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>125</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>187.5</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="D5" t="n">
-        <v>-7.5</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-62.5</v>
-      </c>
-      <c r="F5" t="n">
-        <v>-125</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="E6" t="n">
-        <v>-125</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3465,94 +7318,106 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:P49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
-    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="8" max="8"/>
+    <col width="5" customWidth="1" min="9" max="9"/>
+    <col width="5" customWidth="1" min="10" max="10"/>
+    <col width="5" customWidth="1" min="11" max="11"/>
+    <col width="5" customWidth="1" min="12" max="12"/>
+    <col width="5" customWidth="1" min="13" max="13"/>
+    <col width="5" customWidth="1" min="14" max="14"/>
+    <col width="5" customWidth="1" min="15" max="15"/>
+    <col width="5" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Barra ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Nodo Inicial</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Nodo Final</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Longitud (cm)</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>tita (deg)</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>x_local_x</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>x_local_y</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>x_local_z</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>y_local_x</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>y_local_y</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>y_local_z</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>z_local_x</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>z_local_y</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>z_local_z</t>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Fila</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>C8</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>C11</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>C12</t>
         </is>
       </c>
     </row>
@@ -3567,10 +7432,10 @@
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -3579,84 +7444,96 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>300</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="n">
-        <v>4</v>
-      </c>
-      <c r="C4" t="n">
-        <v>5</v>
-      </c>
-      <c r="D4" t="n">
-        <v>200</v>
-      </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
@@ -3664,19 +7541,19 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -3685,39 +7562,45 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -3729,6 +7612,2212 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="n">
+        <v>8</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="n">
+        <v>9</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1</v>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="n">
+        <v>11</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="n">
+        <v>12</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2</v>
+      </c>
+      <c r="B15" t="n">
+        <v>3</v>
+      </c>
+      <c r="C15" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2</v>
+      </c>
+      <c r="B16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" t="n">
+        <v>4</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B17" t="n">
+        <v>3</v>
+      </c>
+      <c r="C17" t="n">
+        <v>4</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" t="n">
+        <v>3</v>
+      </c>
+      <c r="C18" t="n">
+        <v>4</v>
+      </c>
+      <c r="D18" t="n">
+        <v>5</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D19" t="n">
+        <v>6</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" t="n">
+        <v>3</v>
+      </c>
+      <c r="C20" t="n">
+        <v>4</v>
+      </c>
+      <c r="D20" t="n">
+        <v>7</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" t="n">
+        <v>3</v>
+      </c>
+      <c r="C21" t="n">
+        <v>4</v>
+      </c>
+      <c r="D21" t="n">
+        <v>8</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" t="n">
+        <v>3</v>
+      </c>
+      <c r="C22" t="n">
+        <v>4</v>
+      </c>
+      <c r="D22" t="n">
+        <v>9</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" t="n">
+        <v>3</v>
+      </c>
+      <c r="C23" t="n">
+        <v>4</v>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" t="n">
+        <v>3</v>
+      </c>
+      <c r="C24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D24" t="n">
+        <v>11</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2</v>
+      </c>
+      <c r="B25" t="n">
+        <v>3</v>
+      </c>
+      <c r="C25" t="n">
+        <v>4</v>
+      </c>
+      <c r="D25" t="n">
+        <v>12</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>3</v>
+      </c>
+      <c r="B26" t="n">
+        <v>4</v>
+      </c>
+      <c r="C26" t="n">
+        <v>5</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B27" t="n">
+        <v>4</v>
+      </c>
+      <c r="C27" t="n">
+        <v>5</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>3</v>
+      </c>
+      <c r="B28" t="n">
+        <v>4</v>
+      </c>
+      <c r="C28" t="n">
+        <v>5</v>
+      </c>
+      <c r="D28" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>3</v>
+      </c>
+      <c r="B29" t="n">
+        <v>4</v>
+      </c>
+      <c r="C29" t="n">
+        <v>5</v>
+      </c>
+      <c r="D29" t="n">
+        <v>4</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>3</v>
+      </c>
+      <c r="B30" t="n">
+        <v>4</v>
+      </c>
+      <c r="C30" t="n">
+        <v>5</v>
+      </c>
+      <c r="D30" t="n">
+        <v>5</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>3</v>
+      </c>
+      <c r="B31" t="n">
+        <v>4</v>
+      </c>
+      <c r="C31" t="n">
+        <v>5</v>
+      </c>
+      <c r="D31" t="n">
+        <v>6</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>3</v>
+      </c>
+      <c r="B32" t="n">
+        <v>4</v>
+      </c>
+      <c r="C32" t="n">
+        <v>5</v>
+      </c>
+      <c r="D32" t="n">
+        <v>7</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>3</v>
+      </c>
+      <c r="B33" t="n">
+        <v>4</v>
+      </c>
+      <c r="C33" t="n">
+        <v>5</v>
+      </c>
+      <c r="D33" t="n">
+        <v>8</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>3</v>
+      </c>
+      <c r="B34" t="n">
+        <v>4</v>
+      </c>
+      <c r="C34" t="n">
+        <v>5</v>
+      </c>
+      <c r="D34" t="n">
+        <v>9</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>3</v>
+      </c>
+      <c r="B35" t="n">
+        <v>4</v>
+      </c>
+      <c r="C35" t="n">
+        <v>5</v>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>3</v>
+      </c>
+      <c r="B36" t="n">
+        <v>4</v>
+      </c>
+      <c r="C36" t="n">
+        <v>5</v>
+      </c>
+      <c r="D36" t="n">
+        <v>11</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>3</v>
+      </c>
+      <c r="B37" t="n">
+        <v>4</v>
+      </c>
+      <c r="C37" t="n">
+        <v>5</v>
+      </c>
+      <c r="D37" t="n">
+        <v>12</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>4</v>
+      </c>
+      <c r="B38" t="n">
+        <v>2</v>
+      </c>
+      <c r="C38" t="n">
+        <v>4</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>4</v>
+      </c>
+      <c r="B39" t="n">
+        <v>2</v>
+      </c>
+      <c r="C39" t="n">
+        <v>4</v>
+      </c>
+      <c r="D39" t="n">
+        <v>2</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>4</v>
+      </c>
+      <c r="B40" t="n">
+        <v>2</v>
+      </c>
+      <c r="C40" t="n">
+        <v>4</v>
+      </c>
+      <c r="D40" t="n">
+        <v>3</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>4</v>
+      </c>
+      <c r="B41" t="n">
+        <v>2</v>
+      </c>
+      <c r="C41" t="n">
+        <v>4</v>
+      </c>
+      <c r="D41" t="n">
+        <v>4</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>4</v>
+      </c>
+      <c r="B42" t="n">
+        <v>2</v>
+      </c>
+      <c r="C42" t="n">
+        <v>4</v>
+      </c>
+      <c r="D42" t="n">
+        <v>5</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>4</v>
+      </c>
+      <c r="B43" t="n">
+        <v>2</v>
+      </c>
+      <c r="C43" t="n">
+        <v>4</v>
+      </c>
+      <c r="D43" t="n">
+        <v>6</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>4</v>
+      </c>
+      <c r="B44" t="n">
+        <v>2</v>
+      </c>
+      <c r="C44" t="n">
+        <v>4</v>
+      </c>
+      <c r="D44" t="n">
+        <v>7</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>1</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>4</v>
+      </c>
+      <c r="B45" t="n">
+        <v>2</v>
+      </c>
+      <c r="C45" t="n">
+        <v>4</v>
+      </c>
+      <c r="D45" t="n">
+        <v>8</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>1</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>4</v>
+      </c>
+      <c r="B46" t="n">
+        <v>2</v>
+      </c>
+      <c r="C46" t="n">
+        <v>4</v>
+      </c>
+      <c r="D46" t="n">
+        <v>9</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>4</v>
+      </c>
+      <c r="B47" t="n">
+        <v>2</v>
+      </c>
+      <c r="C47" t="n">
+        <v>4</v>
+      </c>
+      <c r="D47" t="n">
+        <v>10</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>1</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>4</v>
+      </c>
+      <c r="B48" t="n">
+        <v>2</v>
+      </c>
+      <c r="C48" t="n">
+        <v>4</v>
+      </c>
+      <c r="D48" t="n">
+        <v>11</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>1</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>4</v>
+      </c>
+      <c r="B49" t="n">
+        <v>2</v>
+      </c>
+      <c r="C49" t="n">
+        <v>4</v>
+      </c>
+      <c r="D49" t="n">
+        <v>12</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3765,82 +9854,82 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Barra ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Nodo Inicial</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Nodo Final</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Fila</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>C2</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>C3</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>C4</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>C5</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>C6</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>C7</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>C8</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>C9</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>C10</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>C11</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>C12</t>
         </is>
